--- a/ChecklistDeControloDeArtefactos.xlsx
+++ b/ChecklistDeControloDeArtefactos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\LDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FBFDC6-B826-4EAE-88C5-CDB4E94D46A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB0BC92-6ACA-48A7-995E-A4B951BCD1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Milestone 1" sheetId="1" r:id="rId1"/>
@@ -275,9 +275,6 @@
     <t>Diagrama de Sequência (Remarcação de consultas)</t>
   </si>
   <si>
-    <t>Diagrama de Estados (Estado da consulta - Agendada/ Confirmada/ Realizada/ Cancelada)</t>
-  </si>
-  <si>
     <t>Diagrama de Estados (Disponibilidade do médico - Livre / Reservado / Fora de serviço)</t>
   </si>
   <si>
@@ -444,6 +441,9 @@
   </si>
   <si>
     <t>ChecklistDeControloDeArtefactos.xlsx</t>
+  </si>
+  <si>
+    <t>Diagrama de Estados (Estado da consulta - Agendada/ Realizada/ Cancelada)</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1022,7 @@
         <v>45923</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H3" s="4"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>45923</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H4" s="4"/>
     </row>
@@ -1066,7 +1066,7 @@
         <v>45923</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -1088,7 +1088,7 @@
         <v>45923</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H6" s="4"/>
     </row>
@@ -1110,7 +1110,7 @@
         <v>45923</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -1154,7 +1154,7 @@
         <v>45923</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -1198,17 +1198,17 @@
         <v>45923</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>93</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>94</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>23</v>
@@ -1220,7 +1220,7 @@
         <v>45923</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H12" s="4"/>
     </row>
@@ -1306,10 +1306,10 @@
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>42</v>
@@ -1321,7 +1321,7 @@
         <v>45938</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H3" s="12"/>
     </row>
@@ -1343,7 +1343,7 @@
         <v>45938</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H4" s="12"/>
     </row>
@@ -1365,7 +1365,7 @@
         <v>45938</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H5" s="12"/>
     </row>
@@ -1387,7 +1387,7 @@
         <v>45938</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H6" s="12"/>
     </row>
@@ -1409,7 +1409,7 @@
         <v>45938</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H7" s="12"/>
     </row>
@@ -1419,7 +1419,7 @@
         <v>75</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>42</v>
@@ -1431,7 +1431,7 @@
         <v>45938</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H8" s="12"/>
     </row>
@@ -1441,7 +1441,7 @@
         <v>76</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>42</v>
@@ -1453,7 +1453,7 @@
         <v>45938</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H9" s="12"/>
     </row>
@@ -1463,7 +1463,7 @@
         <v>77</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>42</v>
@@ -1475,17 +1475,17 @@
         <v>45938</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>42</v>
@@ -1497,17 +1497,17 @@
         <v>45938</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H11" s="12"/>
     </row>
     <row r="12" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A12" s="10"/>
       <c r="B12" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>42</v>
@@ -1519,17 +1519,17 @@
         <v>45938</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="10"/>
       <c r="B13" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>42</v>
@@ -1541,17 +1541,17 @@
         <v>45938</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
       <c r="B14" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>42</v>
@@ -1563,17 +1563,17 @@
         <v>45938</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="10"/>
       <c r="B15" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>42</v>
@@ -1585,17 +1585,17 @@
         <v>45938</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="10"/>
       <c r="B16" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>42</v>
@@ -1607,17 +1607,17 @@
         <v>45938</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="10"/>
       <c r="B17" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>42</v>
@@ -1629,7 +1629,7 @@
         <v>45938</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H17" s="12"/>
     </row>
@@ -1651,17 +1651,17 @@
         <v>45938</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="10"/>
       <c r="B19" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>42</v>
@@ -1673,17 +1673,17 @@
         <v>45938</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="10"/>
       <c r="B20" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>42</v>
@@ -1695,7 +1695,7 @@
         <v>45938</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H20" s="12"/>
     </row>
@@ -1717,7 +1717,7 @@
         <v>45938</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H21" s="12"/>
     </row>
@@ -1739,7 +1739,7 @@
         <v>45938</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H22" s="12"/>
     </row>
@@ -1760,7 +1760,7 @@
         <v>45938</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1832,7 +1832,7 @@
         <v>45966</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H3" s="12"/>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45966</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H4" s="12"/>
     </row>
@@ -1876,7 +1876,7 @@
         <v>45966</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H5" s="12"/>
     </row>
@@ -1898,7 +1898,7 @@
         <v>45966</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H6" s="12"/>
     </row>
@@ -1920,7 +1920,7 @@
         <v>45966</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H7" s="12"/>
     </row>
@@ -1942,7 +1942,7 @@
         <v>45966</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H8" s="12"/>
     </row>
@@ -1964,7 +1964,7 @@
         <v>45966</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H9" s="12"/>
     </row>
@@ -1986,7 +1986,7 @@
         <v>45966</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H10" s="12"/>
     </row>
@@ -2008,7 +2008,7 @@
         <v>45966</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H11" s="12"/>
     </row>
@@ -2088,7 +2088,7 @@
         <v>45994</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H3" s="4"/>
     </row>
@@ -2110,7 +2110,7 @@
         <v>45994</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H4" s="4"/>
     </row>
@@ -2132,7 +2132,7 @@
         <v>45994</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -2154,7 +2154,7 @@
         <v>45994</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H6" s="4"/>
     </row>
@@ -2176,7 +2176,7 @@
         <v>45994</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -2198,7 +2198,7 @@
         <v>45994</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H8" s="4"/>
     </row>
@@ -2220,7 +2220,7 @@
         <v>45994</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -2242,7 +2242,7 @@
         <v>45994</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H10" s="4"/>
     </row>

--- a/ChecklistDeControloDeArtefactos.xlsx
+++ b/ChecklistDeControloDeArtefactos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\LDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB0BC92-6ACA-48A7-995E-A4B951BCD1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9143DA-C51D-4725-B54F-77682A0EB3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="143">
   <si>
     <t>Nome</t>
   </si>
@@ -140,9 +140,6 @@
     <t>Casos de Uso</t>
   </si>
   <si>
-    <t>Diagrama(s) ER e Dicionário(s) de Dados</t>
-  </si>
-  <si>
     <t>Plano de Testes</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
     <t>Descrição das interações dos utilizadores com o sistema.</t>
   </si>
   <si>
-    <t>Modelo entidade-relação da base de dados e explicação dos atributos.</t>
-  </si>
-  <si>
     <t>Estratégia de testes para validar o sistema.</t>
   </si>
   <si>
@@ -377,18 +371,9 @@
     <t>Arquitetura.docx</t>
   </si>
   <si>
-    <t>/Mockups</t>
-  </si>
-  <si>
-    <t>UseCases.docx</t>
-  </si>
-  <si>
     <t>DiagramasUML.docx</t>
   </si>
   <si>
-    <t>DiagramaER.docx</t>
-  </si>
-  <si>
     <t>RTM.docx</t>
   </si>
   <si>
@@ -401,9 +386,6 @@
     <t>ProductBacklog.docx</t>
   </si>
   <si>
-    <t>CCA.docx</t>
-  </si>
-  <si>
     <t>/Backend</t>
   </si>
   <si>
@@ -444,6 +426,48 @@
   </si>
   <si>
     <t>Diagrama de Estados (Estado da consulta - Agendada/ Realizada/ Cancelada)</t>
+  </si>
+  <si>
+    <t>ChecklistDeControloDeArtefactos.docx</t>
+  </si>
+  <si>
+    <t>Dicionário de Dados</t>
+  </si>
+  <si>
+    <t>Diagrama ER</t>
+  </si>
+  <si>
+    <t>Modelo entidade-relação da base de dados.</t>
+  </si>
+  <si>
+    <t>Explicação dos atributos da base de dados concebida.</t>
+  </si>
+  <si>
+    <t>DicionarioDeDados.docx</t>
+  </si>
+  <si>
+    <t>Diogo</t>
+  </si>
+  <si>
+    <t>André</t>
+  </si>
+  <si>
+    <t>Guilherme</t>
+  </si>
+  <si>
+    <t>Gonçalo</t>
+  </si>
+  <si>
+    <t>Diogo e André</t>
+  </si>
+  <si>
+    <t>Diogo e Guilherme</t>
+  </si>
+  <si>
+    <t>Gonçalo e Diogo</t>
+  </si>
+  <si>
+    <t>Mockups.pdf</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1034,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>23</v>
@@ -1022,7 +1046,7 @@
         <v>45923</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H3" s="4"/>
     </row>
@@ -1044,7 +1068,7 @@
         <v>45923</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H4" s="4"/>
     </row>
@@ -1066,7 +1090,7 @@
         <v>45923</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -1088,7 +1112,7 @@
         <v>45923</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H6" s="4"/>
     </row>
@@ -1098,7 +1122,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>23</v>
@@ -1110,7 +1134,7 @@
         <v>45923</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -1154,7 +1178,7 @@
         <v>45923</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -1186,7 +1210,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>23</v>
@@ -1198,17 +1222,17 @@
         <v>45923</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>23</v>
@@ -1220,7 +1244,7 @@
         <v>45923</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H12" s="4"/>
     </row>
@@ -1260,20 +1284,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A66EA39F-753F-4FFE-94B6-3459E370B3FE}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="8"/>
     <col min="2" max="2" width="38.85546875" style="8" customWidth="1"/>
     <col min="3" max="3" width="54.140625" style="8" customWidth="1"/>
     <col min="4" max="4" width="12.42578125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="8"/>
+    <col min="5" max="5" width="10.7109375" style="8" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" style="8" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1306,13 +1330,13 @@
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>22</v>
@@ -1321,7 +1345,7 @@
         <v>45938</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H3" s="12"/>
     </row>
@@ -1333,8 +1357,8 @@
       <c r="C4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>42</v>
+      <c r="D4" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>22</v>
@@ -1343,29 +1367,29 @@
         <v>45938</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="10"/>
       <c r="B5" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="F5" s="19">
         <v>45938</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H5" s="12"/>
     </row>
@@ -1375,19 +1399,19 @@
         <v>31</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="F6" s="19">
         <v>45938</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="H6" s="12"/>
     </row>
@@ -1397,370 +1421,392 @@
         <v>32</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="F7" s="19">
         <v>45938</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H7" s="12"/>
     </row>
     <row r="8" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="10"/>
       <c r="B8" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F8" s="19">
         <v>45938</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="10"/>
       <c r="B9" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F9" s="19">
         <v>45938</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="10"/>
       <c r="B10" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F10" s="19">
         <v>45938</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F11" s="19">
         <v>45938</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H11" s="12"/>
     </row>
     <row r="12" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A12" s="10"/>
       <c r="B12" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F12" s="19">
         <v>45938</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="10"/>
       <c r="B13" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F13" s="19">
         <v>45938</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
       <c r="B14" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F14" s="19">
         <v>45938</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="10"/>
       <c r="B15" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F15" s="19">
         <v>45938</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="10"/>
       <c r="B16" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>42</v>
+        <v>93</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F16" s="19">
         <v>45938</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="10"/>
       <c r="B17" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>42</v>
+        <v>89</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F17" s="19">
         <v>45938</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H17" s="12"/>
     </row>
-    <row r="18" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="10"/>
       <c r="B18" s="5" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>42</v>
+        <v>132</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F18" s="19">
         <v>45938</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="10"/>
       <c r="B19" s="5" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>42</v>
+        <v>133</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="F19" s="19">
         <v>45938</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="10"/>
       <c r="B20" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="F20" s="19">
         <v>45938</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="10"/>
       <c r="B21" s="5" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>42</v>
+        <v>96</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>22</v>
+        <v>141</v>
       </c>
       <c r="F21" s="19">
         <v>45938</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H21" s="12"/>
     </row>
-    <row r="22" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="10"/>
       <c r="B22" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="F22" s="19">
         <v>45938</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H22" s="12"/>
     </row>
-    <row r="23" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="10"/>
       <c r="B23" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="F23" s="19">
         <v>45938</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
+      </c>
+      <c r="H23" s="12"/>
+    </row>
+    <row r="24" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="19">
+        <v>45938</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1817,13 +1863,13 @@
     <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>22</v>
@@ -1832,20 +1878,20 @@
         <v>45966</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
       <c r="B4" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>22</v>
@@ -1854,20 +1900,20 @@
         <v>45966</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H4" s="12"/>
     </row>
     <row r="5" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="10"/>
       <c r="B5" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>22</v>
@@ -1876,20 +1922,20 @@
         <v>45966</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H5" s="12"/>
     </row>
     <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="10"/>
       <c r="B6" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>22</v>
@@ -1898,20 +1944,20 @@
         <v>45966</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H6" s="12"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="10"/>
       <c r="B7" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>22</v>
@@ -1920,20 +1966,20 @@
         <v>45966</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H7" s="12"/>
     </row>
     <row r="8" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="10"/>
       <c r="B8" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>22</v>
@@ -1942,20 +1988,20 @@
         <v>45966</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="10"/>
       <c r="B9" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>22</v>
@@ -1964,20 +2010,20 @@
         <v>45966</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="10"/>
       <c r="B10" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>22</v>
@@ -1986,20 +2032,20 @@
         <v>45966</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>22</v>
@@ -2008,7 +2054,7 @@
         <v>45966</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H11" s="12"/>
     </row>
@@ -2073,13 +2119,13 @@
     <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>22</v>
@@ -2088,20 +2134,20 @@
         <v>45994</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>22</v>
@@ -2110,20 +2156,20 @@
         <v>45994</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>22</v>
@@ -2132,20 +2178,20 @@
         <v>45994</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>22</v>
@@ -2154,20 +2200,20 @@
         <v>45994</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>22</v>
@@ -2176,20 +2222,20 @@
         <v>45994</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>22</v>
@@ -2198,20 +2244,20 @@
         <v>45994</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>22</v>
@@ -2220,20 +2266,20 @@
         <v>45994</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>22</v>
@@ -2242,7 +2288,7 @@
         <v>45994</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H10" s="4"/>
     </row>

--- a/ChecklistDeControloDeArtefactos.xlsx
+++ b/ChecklistDeControloDeArtefactos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\LDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB0BC92-6ACA-48A7-995E-A4B951BCD1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA95739-B09D-45E1-A013-E9472A462C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
   </bookViews>
@@ -1750,8 +1750,8 @@
       <c r="C23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>42</v>
+      <c r="D23" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>22</v>

--- a/ChecklistDeControloDeArtefactos.xlsx
+++ b/ChecklistDeControloDeArtefactos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\LDS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA95739-B09D-45E1-A013-E9472A462C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2E8660-CA06-4657-B8C8-D0466FCB47A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Milestone 1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="136">
   <si>
     <t>Nome</t>
   </si>
@@ -140,9 +140,6 @@
     <t>Casos de Uso</t>
   </si>
   <si>
-    <t>Diagrama(s) ER e Dicionário(s) de Dados</t>
-  </si>
-  <si>
     <t>Plano de Testes</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
     <t>Descrição das interações dos utilizadores com o sistema.</t>
   </si>
   <si>
-    <t>Modelo entidade-relação da base de dados e explicação dos atributos.</t>
-  </si>
-  <si>
     <t>Estratégia de testes para validar o sistema.</t>
   </si>
   <si>
@@ -377,18 +371,12 @@
     <t>Arquitetura.docx</t>
   </si>
   <si>
-    <t>/Mockups</t>
-  </si>
-  <si>
     <t>UseCases.docx</t>
   </si>
   <si>
     <t>DiagramasUML.docx</t>
   </si>
   <si>
-    <t>DiagramaER.docx</t>
-  </si>
-  <si>
     <t>RTM.docx</t>
   </si>
   <si>
@@ -398,12 +386,6 @@
     <t>PlanoDeTestes.docx</t>
   </si>
   <si>
-    <t>ProductBacklog.docx</t>
-  </si>
-  <si>
-    <t>CCA.docx</t>
-  </si>
-  <si>
     <t>/Backend</t>
   </si>
   <si>
@@ -444,6 +426,27 @@
   </si>
   <si>
     <t>Diagrama de Estados (Estado da consulta - Agendada/ Realizada/ Cancelada)</t>
+  </si>
+  <si>
+    <t>Diagrama(s) ER</t>
+  </si>
+  <si>
+    <t>Dicionário(s) de Dados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo entidade-relação da base de dados </t>
+  </si>
+  <si>
+    <t>DicionárioDeDados.docx</t>
+  </si>
+  <si>
+    <t>Explicação dos atributos do diagrama ER.</t>
+  </si>
+  <si>
+    <t>ProductBacklog.xlsx</t>
+  </si>
+  <si>
+    <t>Mockups.pdf</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1013,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>23</v>
@@ -1022,7 +1025,7 @@
         <v>45923</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H3" s="4"/>
     </row>
@@ -1044,7 +1047,7 @@
         <v>45923</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H4" s="4"/>
     </row>
@@ -1066,7 +1069,7 @@
         <v>45923</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -1088,7 +1091,7 @@
         <v>45923</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H6" s="4"/>
     </row>
@@ -1098,7 +1101,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>23</v>
@@ -1110,7 +1113,7 @@
         <v>45923</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -1154,7 +1157,7 @@
         <v>45923</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -1186,7 +1189,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>23</v>
@@ -1198,17 +1201,17 @@
         <v>45923</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>23</v>
@@ -1220,7 +1223,7 @@
         <v>45923</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H12" s="4"/>
     </row>
@@ -1260,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A66EA39F-753F-4FFE-94B6-3459E370B3FE}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="8"/>
@@ -1306,13 +1309,13 @@
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>42</v>
+        <v>106</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>22</v>
@@ -1321,7 +1324,7 @@
         <v>45938</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H3" s="12"/>
     </row>
@@ -1333,8 +1336,8 @@
       <c r="C4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>42</v>
+      <c r="D4" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>22</v>
@@ -1343,7 +1346,7 @@
         <v>45938</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H4" s="12"/>
     </row>
@@ -1353,10 +1356,10 @@
         <v>30</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>22</v>
@@ -1365,7 +1368,7 @@
         <v>45938</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H5" s="12"/>
     </row>
@@ -1375,10 +1378,10 @@
         <v>31</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>22</v>
@@ -1387,7 +1390,7 @@
         <v>45938</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="H6" s="12"/>
     </row>
@@ -1397,10 +1400,10 @@
         <v>32</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>22</v>
@@ -1409,20 +1412,20 @@
         <v>45938</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H7" s="12"/>
     </row>
     <row r="8" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="10"/>
       <c r="B8" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>81</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>22</v>
@@ -1431,20 +1434,20 @@
         <v>45938</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="10"/>
       <c r="B9" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>42</v>
+        <v>82</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>22</v>
@@ -1453,20 +1456,20 @@
         <v>45938</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="10"/>
       <c r="B10" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>42</v>
+        <v>83</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>22</v>
@@ -1475,20 +1478,20 @@
         <v>45938</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>42</v>
+        <v>84</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>22</v>
@@ -1497,20 +1500,20 @@
         <v>45938</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H11" s="12"/>
     </row>
     <row r="12" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A12" s="10"/>
       <c r="B12" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>42</v>
+        <v>85</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>22</v>
@@ -1519,20 +1522,20 @@
         <v>45938</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="10"/>
       <c r="B13" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>42</v>
+        <v>86</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>22</v>
@@ -1541,20 +1544,20 @@
         <v>45938</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
       <c r="B14" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>42</v>
+        <v>87</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>22</v>
@@ -1563,20 +1566,20 @@
         <v>45938</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="10"/>
       <c r="B15" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>42</v>
+        <v>88</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>22</v>
@@ -1585,20 +1588,20 @@
         <v>45938</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="10"/>
       <c r="B16" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>42</v>
+        <v>93</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>22</v>
@@ -1607,20 +1610,20 @@
         <v>45938</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="10"/>
       <c r="B17" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>42</v>
+        <v>89</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>22</v>
@@ -1629,20 +1632,20 @@
         <v>45938</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H17" s="12"/>
     </row>
-    <row r="18" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="10"/>
       <c r="B18" s="5" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>42</v>
+        <v>131</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>22</v>
@@ -1651,20 +1654,20 @@
         <v>45938</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="10"/>
       <c r="B19" s="5" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>42</v>
+        <v>133</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>22</v>
@@ -1673,20 +1676,20 @@
         <v>45938</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="10"/>
       <c r="B20" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>42</v>
+        <v>97</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>22</v>
@@ -1695,20 +1698,20 @@
         <v>45938</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="10"/>
       <c r="B21" s="5" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>42</v>
+        <v>96</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>22</v>
@@ -1717,20 +1720,20 @@
         <v>45938</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H21" s="12"/>
     </row>
-    <row r="22" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="10"/>
       <c r="B22" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>22</v>
@@ -1739,16 +1742,17 @@
         <v>45938</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H22" s="12"/>
     </row>
-    <row r="23" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="10"/>
       <c r="B23" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>23</v>
@@ -1760,7 +1764,28 @@
         <v>45938</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>120</v>
+        <v>134</v>
+      </c>
+      <c r="H23" s="12"/>
+    </row>
+    <row r="24" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="19">
+        <v>45938</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1817,13 +1842,13 @@
     <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>22</v>
@@ -1832,20 +1857,20 @@
         <v>45966</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
       <c r="B4" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>22</v>
@@ -1854,20 +1879,20 @@
         <v>45966</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H4" s="12"/>
     </row>
     <row r="5" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="10"/>
       <c r="B5" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>22</v>
@@ -1876,20 +1901,20 @@
         <v>45966</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H5" s="12"/>
     </row>
     <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="10"/>
       <c r="B6" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>22</v>
@@ -1898,20 +1923,20 @@
         <v>45966</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H6" s="12"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="10"/>
       <c r="B7" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>22</v>
@@ -1920,20 +1945,20 @@
         <v>45966</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H7" s="12"/>
     </row>
     <row r="8" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="10"/>
       <c r="B8" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>22</v>
@@ -1942,20 +1967,20 @@
         <v>45966</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="10"/>
       <c r="B9" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>22</v>
@@ -1964,20 +1989,20 @@
         <v>45966</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="10"/>
       <c r="B10" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>22</v>
@@ -1986,20 +2011,20 @@
         <v>45966</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>22</v>
@@ -2008,7 +2033,7 @@
         <v>45966</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H11" s="12"/>
     </row>
@@ -2073,13 +2098,13 @@
     <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>22</v>
@@ -2088,20 +2113,20 @@
         <v>45994</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>22</v>
@@ -2110,20 +2135,20 @@
         <v>45994</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>22</v>
@@ -2132,20 +2157,20 @@
         <v>45994</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>22</v>
@@ -2154,20 +2179,20 @@
         <v>45994</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>22</v>
@@ -2176,20 +2201,20 @@
         <v>45994</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>22</v>
@@ -2198,20 +2223,20 @@
         <v>45994</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>22</v>
@@ -2220,20 +2245,20 @@
         <v>45994</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>22</v>
@@ -2242,7 +2267,7 @@
         <v>45994</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H10" s="4"/>
     </row>
